--- a/data/trans_dic/IP13_R2_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R2_2023-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas</t>
+          <t>Menores que limitaron su actividad por síntomas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,77</t>
+          <t>0,67; 5,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 11,62</t>
+          <t>1,94; 12,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 7,74</t>
+          <t>1,79; 7,63</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 7,9</t>
+          <t>2,45; 7,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 9,61</t>
+          <t>3,78; 10,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 7,42</t>
+          <t>3,48; 7,28</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 8,32</t>
+          <t>2,4; 8,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,94; 8,33</t>
+          <t>2,56; 8,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 7,02</t>
+          <t>3,11; 7,41</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 6,11</t>
+          <t>2,08; 6,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,23</t>
+          <t>2,0; 6,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,31</t>
+          <t>2,47; 5,15</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,46</t>
+          <t>2,86; 5,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,2</t>
+          <t>3,45; 6,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 5,51</t>
+          <t>3,61; 5,43</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por síntomas (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1528</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3255</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4783</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>386; 3445</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1192; 7485</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2125; 9081</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>7017</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11115</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18132</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3901; 12117</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6871; 18383</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>11883; 24841</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>8203</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10724</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18927</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4150; 13972</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5431; 17577</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11986; 28567</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>10110</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11459</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21569</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>5734; 17807</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>6096; 19247</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>14322; 29900</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>26858</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>36553</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>63411</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>19011; 36467</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>26271; 47471</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>51509; 77482</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP13_R2_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R2_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas (tasa de respuesta: 99,95%)</t>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por síntomas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,99</t>
+          <t>0,67; 6,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 12,18</t>
+          <t>1,69; 12,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 7,63</t>
+          <t>1,95; 7,79</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 7,61</t>
+          <t>2,34; 7,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,78; 10,11</t>
+          <t>3,54; 9,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,48; 7,28</t>
+          <t>3,64; 7,51</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 8,07</t>
+          <t>2,59; 8,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,56; 8,27</t>
+          <t>2,56; 8,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,11; 7,41</t>
+          <t>3,05; 7,38</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,46</t>
+          <t>2,05; 6,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,3</t>
+          <t>1,97; 6,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,15</t>
+          <t>2,52; 5,26</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,48</t>
+          <t>2,84; 5,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,24</t>
+          <t>3,61; 6,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 5,43</t>
+          <t>3,59; 5,46</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas (tasa de respuesta: 99,95%)</t>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por síntomas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>386; 3445</t>
+          <t>384; 3460</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1192; 7485</t>
+          <t>1038; 7476</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2125; 9081</t>
+          <t>2324; 9270</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3901; 12117</t>
+          <t>3720; 11773</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6871; 18383</t>
+          <t>6433; 17263</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11883; 24841</t>
+          <t>12415; 25614</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4150; 13972</t>
+          <t>4474; 14230</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5431; 17577</t>
+          <t>5439; 17324</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11986; 28567</t>
+          <t>11765; 28442</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5734; 17807</t>
+          <t>5649; 16808</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6096; 19247</t>
+          <t>6032; 18515</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14322; 29900</t>
+          <t>14631; 30578</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19011; 36467</t>
+          <t>18874; 35042</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>26271; 47471</t>
+          <t>27485; 48516</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51509; 77482</t>
+          <t>51166; 77859</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP13_R2_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R2_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,02</t>
+          <t>2,04; 12,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 12,17</t>
+          <t>0,65; 6,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,79</t>
+          <t>1,85; 7,8</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 7,39</t>
+          <t>3,69; 9,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 9,49</t>
+          <t>2,35; 7,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 7,51</t>
+          <t>3,42; 7,09</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 8,22</t>
+          <t>3,12; 8,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,56; 8,15</t>
+          <t>2,56; 8,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 7,38</t>
+          <t>3,33; 7,23</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,1</t>
+          <t>2,12; 6,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 6,06</t>
+          <t>2,46; 6,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,26</t>
+          <t>2,75; 5,65</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,27</t>
+          <t>3,71; 6,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,37</t>
+          <t>3,01; 5,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,59; 5,46</t>
+          <t>3,72; 5,6</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4204</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>384; 3460</t>
+          <t>1032; 6215</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1038; 7476</t>
+          <t>341; 3341</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2324; 9270</t>
+          <t>1897; 8003</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7017</t>
+          <t>9176</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11115</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18132</t>
+          <t>15423</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3720; 11773</t>
+          <t>5795; 14928</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6433; 17263</t>
+          <t>3416; 11086</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12415; 25614</t>
+          <t>10340; 21445</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10724</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18927</t>
+          <t>19072</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4474; 14230</t>
+          <t>6243; 17866</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5439; 17324</t>
+          <t>4476; 14525</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11765; 28442</t>
+          <t>12471; 27093</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>11368</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>10407</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21569</t>
+          <t>21774</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5649; 16808</t>
+          <t>6191; 18652</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6032; 18515</t>
+          <t>6309; 16836</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14631; 30578</t>
+          <t>15085; 31011</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>26858</t>
+          <t>34234</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>36553</t>
+          <t>26239</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63411</t>
+          <t>60473</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18874; 35042</t>
+          <t>26014; 44933</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27485; 48516</t>
+          <t>18945; 35016</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51166; 77859</t>
+          <t>49431; 74402</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP13_R2_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R2_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por síntomas (tasa de respuesta: 99,95%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4,1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2,04; 12,3</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,65; 6,41</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,85; 7,8</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>5,85%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>3,69; 9,51</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2,35; 7,62</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3,42; 7,09</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>3,12; 8,93</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2,56; 8,32</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>3,33; 7,23</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2,12; 6,37</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2,46; 6,56</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2,75; 5,65</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>3,71; 6,42</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>3,01; 5,57</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3,72; 5,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.05698431319134267</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.02541974431691775</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.04096334758325535</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1324</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4204</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.02042519554100783</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.006545168942753665</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.01848435253803279</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1032; 6215</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>341; 3341</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1897; 8003</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.1229826063901356</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.06414824621080643</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.07798437914228933</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.05845069133485935</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.04292760801556842</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.05098337349962507</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>9176</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6247</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>15423</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.0369143996517235</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.02347443890016322</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.03418019877185115</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>5795; 14928</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3416; 11086</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>10340; 21445</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.09509012708779858</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.07618083229082763</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.07089189089404656</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.05402100892381295</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.04729708097807566</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.05088736499729271</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>10811</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>8261</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>19072</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.0311931780070604</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.02562426007936234</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.03327268177701591</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>6243; 17866</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4476; 14525</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12471; 27093</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.08927513811352691</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.08315330142584972</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.07228808835034466</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.03884475900080929</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.04056336237193393</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.03964759045190355</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>11368</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>10407</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>21774</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.02115690718134533</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.02459260007057689</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.02746760462422872</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>6191; 18652</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>6309; 16836</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>15085; 31011</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.06373513907937145</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.06562338299379858</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.05646567866572888</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.04888587545735911</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.04172648469626149</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.04549864135286093</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>34234</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>26239</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>60473</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.03714727948428735</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.03012678807661155</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.03719056314963567</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>26014; 44933</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>18945; 35016</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>49431; 74402</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.06416299531432031</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.05568360607174268</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.05597802633771914</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por síntomas (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1324</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>4204</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1032</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>341</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>6215</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>3341</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>8003</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>9176</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>6247</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>15423</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>5795</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>3416</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>10340</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>14928</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>11086</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>21445</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>10811</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>8261</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>19072</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>6243</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>4476</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>12471</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>17866</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>14525</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>27093</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>11368</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>10407</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>21774</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>6191</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>6309</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>15085</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>18652</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>16836</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>31011</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>34234</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>26239</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>60473</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>26014</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>18945</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>49431</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>44933</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>35016</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>74402</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>